--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D13DEA1-DA92-4C21-BBB6-6D9E4BF5F41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CAFFD5-F45F-47AE-B0E1-9794A99EE495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="5040" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,15 +67,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,2,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003,3,0</t>
+    <t>1001,1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,2,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003,3,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70401,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70501,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70701,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70901,1,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,17 +433,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,11 +456,12 @@
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -453,11 +471,11 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -467,11 +485,11 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -484,102 +502,125 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
+        <v>3900001</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C1:F1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CAFFD5-F45F-47AE-B0E1-9794A99EE495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D24ED0-9A55-4AD7-8A02-F844BAF33B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,19 +79,33 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>70401,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70501,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70701,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70901,1,100</t>
+    <t>迅速/刚聚/力增/武增</t>
+  </si>
+  <si>
+    <t>武增/术增/迅速/巧增</t>
+  </si>
+  <si>
+    <t>10041,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10051,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10071,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10091,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10101,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10111,1,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -441,7 +455,8 @@
     <col min="3" max="3" width="33.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -536,33 +551,49 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
-        <v>3900001</v>
+        <v>200001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="B9" s="2">
+        <v>200002</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D24ED0-9A55-4AD7-8A02-F844BAF33B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B72749-41C3-495B-AEF8-46CCD6DC96B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,26 @@
   </si>
   <si>
     <t>10111,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20031,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20041,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20051,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20061,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封穴↑/封穴↓/封穴←/封穴→</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,13 +616,27 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="B10" s="2">
+        <v>200003</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B72749-41C3-495B-AEF8-46CCD6DC96B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06484FF-301E-4433-82C3-EB10889E9634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,6 +126,25 @@
   </si>
   <si>
     <t>封穴↑/封穴↓/封穴←/封穴→</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1层武增1层力增1层巧增</t>
+  </si>
+  <si>
+    <t>2层武增2层力增2层巧增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10071,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10091,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10111,2,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,22 +658,46 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="B11" s="2">
+        <v>200004</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>200005</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -1,31 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06484FF-301E-4433-82C3-EB10889E9634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914329A8-E417-4439-987A-FD39CABCF6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="35565" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,6 +154,42 @@
   </si>
   <si>
     <t>10111,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30291,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30301,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30311,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平|彻|起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2封穴↑|2封穴↓|2封穴←|2封穴→</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20031,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20041,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20051,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20061,2,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +536,7 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="1" customWidth="1"/>
     <col min="4" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" bestFit="1" customWidth="1"/>
@@ -700,22 +745,47 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="B13" s="2">
+        <v>200006</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="B14" s="2">
+        <v>200007</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914329A8-E417-4439-987A-FD39CABCF6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D148550A-D80B-431B-86F8-8EF54FE315E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="35565" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +190,26 @@
   </si>
   <si>
     <t>20061,2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机一种毒向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20241,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20251,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20261,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20271,1,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -788,13 +808,27 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="B15" s="2">
+        <v>200008</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D148550A-D80B-431B-86F8-8EF54FE315E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17FDFF-A280-4BB5-B129-34A2608DD46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -211,6 +211,33 @@
   <si>
     <t>20271,1,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10081,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（迅速/力增/技增/术增/武增/巧增）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10031,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（力增、武增、反击、迅速、巧增）</t>
   </si>
 </sst>
 </file>
@@ -260,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -270,6 +297,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,19 +581,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.375" style="1" customWidth="1"/>
     <col min="4" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="7" max="8" width="13.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,25 +607,32 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -604,11 +642,11 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -621,12 +659,12 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -634,8 +672,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -643,8 +683,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -652,8 +694,10 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>200001</v>
       </c>
@@ -669,14 +713,16 @@
       <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>200002</v>
       </c>
@@ -692,14 +738,16 @@
       <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>200003</v>
       </c>
@@ -715,14 +763,16 @@
       <c r="F10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>200004</v>
       </c>
@@ -736,14 +786,16 @@
         <v>20</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>200005</v>
       </c>
@@ -757,14 +809,16 @@
         <v>30</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>200006</v>
       </c>
@@ -777,14 +831,14 @@
       <c r="E13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="2">
+      <c r="I13" s="2">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>200007</v>
       </c>
@@ -800,14 +854,16 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>200008</v>
       </c>
@@ -823,16 +879,74 @@
       <c r="F15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C1:F1"/>
+  <mergeCells count="2">
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/#CommonPoolConfig.xlsx
+++ b/Luban/Config/Datas/#CommonPoolConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17FDFF-A280-4BB5-B129-34A2608DD46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E6B5D3-B8CB-41B7-BCA9-2896DCD52C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,6 +238,14 @@
   </si>
   <si>
     <t>（力增、武增、反击、迅速、巧增）</t>
+  </si>
+  <si>
+    <t>200011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得1层武增/术增/力增/技增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -296,10 +304,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -601,14 +609,14 @@
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
@@ -620,14 +628,14 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="1" t="s">
         <v>4</v>
       </c>
@@ -889,7 +897,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -918,7 +926,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -941,6 +949,29 @@
       </c>
       <c r="J17" s="1" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
